--- a/Excel/stocks-to-input.xlsx
+++ b/Excel/stocks-to-input.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,7 +443,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAM</t>
+          <t>BANPU</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BANPU</t>
+          <t>BPP</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -463,260 +463,10 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BEM</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BKIH</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BPP</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CRC</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DCON</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GUNKUL</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>HFT</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>HTC</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>IMH</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>KBANK</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>LALIN</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ONEE</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>RBF</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SAWAD</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>SIRI</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>SPRC</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>SSP</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>SUPER</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TSE</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TYCN</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>UTP</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>VIBHA</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>WICE</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
+      <c r="B4" t="n">
         <v>3</v>
       </c>
     </row>
